--- a/daily_matches/job_matches_2026-04-06.xlsx
+++ b/daily_matches/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SENIOR DATA SCIENTIST – ANALYTICS AND AI DATA</t>
+          <t>Senior Data Scientist – Analytics and AI Data</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,82 +491,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43c854614666aac</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cloud Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d120b25eec762a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist II - AI for Analytics</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Instacart</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, PyTorch, Git, Snowflake, Matplotlib, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78f4d247249e68b7</t>
+          <t>https://www.indeed.com/viewjob?jk=221623f7394c7927</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-06.xlsx
+++ b/daily_matches/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Analytics and AI Data</t>
+          <t>UI/UX Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Louis Vuitton</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, S3, CI/CD, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Qlik</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=339f2763f37d72cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Cloud/Backend - SCP (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Kafka, Cassandra, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38b0ae1ffd78b66d</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Digital Health And Behavior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GAP Solutions, Inc.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Hugging Face, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=221623f7394c7927</t>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f607baf5f413f73a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-06.xlsx
+++ b/daily_matches/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Genesys Cloud GenAI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Hugging Face, Prompt Engineering, S3, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4735299b123e3950</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qlik</t>
+          <t>Denali Advanced Integration / 3MD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Optimization</t>
+          <t>RAG, FastAPI, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=339f2763f37d72cb</t>
+          <t>https://www.indeed.com/viewjob?jk=78117cab3c3fc0ee</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud/Backend - SCP (Hybrid)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Qbtech</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Kafka, Cassandra, Python, R, Java, Scala</t>
+          <t>Data Scientist, S3, Data Lake, PySpark, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,112 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b0ae1ffd78b66d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c14d180cd784ef</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Digital Health And Behavior Data Scientist</t>
+          <t>Senior Software Engineer, Core AI Software</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GAP Solutions, Inc.</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Keras, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ba348de63350b88</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tech Interacts Inc</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cef499ceadaa792</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AI Engineer (Hopkins, MN)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Digi International</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, Hugging Face, TensorFlow, PyTorch, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f607baf5f413f73a</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, TensorFlow, PyTorch, Git, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20bf31ba60bc6076</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-06.xlsx
+++ b/daily_matches/job_matches_2026-04-06.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Genesys Cloud GenAI Engineer</t>
+          <t>AI Software Engineer (GenAI/RAG/Azure AI Foundry)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>The Phia Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Hugging Face, Prompt Engineering, S3, Docker, Kubernetes</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Azure ML, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4735299b123e3950</t>
+          <t>https://www.indeed.com/viewjob?jk=35725eea5943b873</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Senior MLOps Engineer - Analytics &amp; AI - R&amp;D - Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Denali Advanced Integration / 3MD</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Athena, Kubernetes, Jenkins, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78117cab3c3fc0ee</t>
+          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qbtech</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Data Lake, PySpark, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c14d180cd784ef</t>
+          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Core AI Software</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Keras, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba348de63350b88</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>Bragg Companies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, Python, SQL, R, Java</t>
+          <t>RAG, Data Lake, Git, Databricks, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cef499ceadaa792</t>
+          <t>https://www.indeed.com/viewjob?jk=feeb798c598ea232</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer (Hopkins, MN)</t>
+          <t>Software Engineer II - Tester</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Digi International</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, TensorFlow, PyTorch, Git, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bf31ba60bc6076</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f16ac9b1b57cca</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-06.xlsx
+++ b/daily_matches/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Software Engineer (GenAI/RAG/Azure AI Foundry)</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Phia Group</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Azure ML, FastAPI, Docker</t>
+          <t>RAG, S3, Glue, Redshift, Data Lake, Kinesis, Apache Airflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35725eea5943b873</t>
+          <t>https://www.indeed.com/viewjob?jk=31364c52fe931267</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer - Analytics &amp; AI - R&amp;D - Engineering</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>KUBRA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Athena, Kubernetes, Jenkins, Terraform, Git, Snowflake</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, AWS SageMaker, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
+          <t>https://www.indeed.com/viewjob?jk=12ee98f808617b3b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, Python</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ce78edc5ea8691</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
+          <t>RAG, S3, Glue, Redshift, MLflow, Git, Databricks, Redshift, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Software Engineer II - Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bragg Companies</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Databricks, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,322 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feeb798c598ea232</t>
+          <t>https://www.indeed.com/viewjob?jk=2429610d97c33cfd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II - Tester</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>S3, Glue, Redshift, CI/CD, Git, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LLM Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Health Business Solutions</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, MLflow, CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AWS Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, AWS SageMaker, S3, EC2, Glue, CI/CD, Jenkins, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40585d0392b72020</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Scientist / Generative AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Expertshub</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed655252edeea719</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>American National Bank of Texas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e099790f917f312a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Java Full Stack Engineer (contract)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f16ac9b1b57cca</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Kubernetes, AKS, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a97988968d09feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Expertshub</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ad3f1b610f1a070</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software AI Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SqlDBM</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Snowflake, Databricks, PostgreSQL, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48c0d6340fce7ab8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer - Hybrid Onsite</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, XGBoost, Docker, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=131e9be745b25a8b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-06.xlsx
+++ b/daily_matches/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Senior VR/XR &amp; Computer Vision Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>IVN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Data Lake, Kinesis, Apache Airflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Gemini, Copilot, TensorFlow, PyTorch, OpenCV, S3, EC2, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31364c52fe931267</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe26087c7f2c3c7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KUBRA</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Clarks Summit, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, AWS SageMaker, CI/CD, Python, SQL, R</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ee98f808617b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Python, SQL</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ce78edc5ea8691</t>
+          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, MLflow, Git, Databricks, Redshift, SQL, R</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer II - Identity &amp; Access Management</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2429610d97c33cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>AI Product Operator - Intern</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, CI/CD, Git, Redshift, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, Copilot, Pinecone, Prompt Engineering, FastAPI, Docker, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=ade938a3ecc6198f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LLM Operations Engineer</t>
+          <t>AI Software Developer / Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, MLflow, CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>LangChain, RAG, Hugging Face, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+          <t>https://www.indeed.com/viewjob?jk=b82ff289db69c27d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Software Application Engineer/Surgical Robotics - OTTAVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, S3, EC2, Glue, CI/CD, Jenkins, Terraform, R, Scala</t>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, CI/CD, Git, Power BI, Quicksight, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40585d0392b72020</t>
+          <t>https://www.indeed.com/viewjob?jk=e5955bea45ef93e0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist / Generative AI Data Engineer</t>
+          <t>Senior AI Product Engineer | Growth and Transformation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed655252edeea719</t>
+          <t>https://www.indeed.com/viewjob?jk=f345c8973f89d612</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American National Bank of Texas</t>
+          <t>AlohaABA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, R, A/B Testing</t>
+          <t>AI Engineer, RAG, Copilot, Hugging Face, Docker, Kubernetes, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e099790f917f312a</t>
+          <t>https://www.indeed.com/viewjob?jk=586b01e5fb4ba966</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Engineer (contract)</t>
+          <t>AI/MLOps Architect - R&amp;D IT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Driscoll's</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Watsonville, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kubernetes, AKS, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a97988968d09feb</t>
+          <t>https://www.indeed.com/viewjob?jk=1a566d06ed5f6179</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Redshift, Data Lake, Snowflake, Redshift, Kafka, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad3f1b610f1a070</t>
+          <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Senior ML/LLM Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SqlDBM</t>
+          <t>U.S. Renal Care</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Snowflake, Databricks, PostgreSQL, SQL, R, Optimization</t>
+          <t>RAG, Copilot, Pinecone, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,147 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c0d6340fce7ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=a88b39030682b636</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Hybrid Onsite</t>
+          <t>Senior Backend Python Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>3MD Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe103858c74b7951</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Machine Learning Research Scientist/Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EDDA TECHNOLOGY, INC.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, XGBoost, Docker, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=131e9be745b25a8b</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Keras, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa77201670c86968</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Intern- Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Symbotic</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b946ca87ec47098e</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fall Co-op, Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Symbotic</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac52f0877fad9d37</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-06.xlsx
+++ b/daily_matches/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior VR/XR &amp; Computer Vision Software Engineer</t>
+          <t>AI Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IVN</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gemini, Copilot, TensorFlow, PyTorch, OpenCV, S3, EC2, FastAPI, Docker, Kubernetes</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe26087c7f2c3c7</t>
+          <t>https://www.indeed.com/viewjob?jk=76545ebacbf0ef00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Intern - Data Engineer - Summer 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Acxiom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Clarks Summit, PA, US USA</t>
+          <t>Conway, AR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Data Scientist, S3, BigQuery, Data Lake, AKS, Apache Airflow, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
+          <t>https://www.indeed.com/viewjob?jk=338baa6df1016586</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Junior Automation Tester (AI enabled Testing)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
+          <t>https://www.indeed.com/viewjob?jk=31c5a628a0bbcd11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Junior Automation Tester (AI enabled Testing)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
+          <t>https://www.indeed.com/viewjob?jk=f99abb391ef4c38f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Junior Automation Tester (AI enabled Testing)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, NoSQL</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=85aec2fe5dbdec6e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Product Operator - Intern</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Pinecone, Prompt Engineering, FastAPI, Docker, Git, PostgreSQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade938a3ecc6198f</t>
+          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Software Developer / Engineer</t>
+          <t>Software Engineer III - Full Stack + AWS + Elastic / Open Search</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Hugging Face, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+          <t>RAG, S3, EC2, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b82ff289db69c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ce76eb1050277d8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Application Engineer/Surgical Robotics - OTTAVA</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Data Lake, Docker, CI/CD, Git, Power BI, Quicksight, Python, SQL</t>
+          <t>Copilot, ChromaDB, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5955bea45ef93e0</t>
+          <t>https://www.indeed.com/viewjob?jk=84da7523f67ecb79</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Product Engineer | Growth and Transformation</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>FireMon</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python</t>
+          <t>RAG, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f345c8973f89d612</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9f14ac4c33a585</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Applied AI &amp; Analytics Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AlohaABA</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Hugging Face, Docker, Kubernetes, Git, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Snowflake, PostgreSQL, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586b01e5fb4ba966</t>
+          <t>https://www.indeed.com/viewjob?jk=be6c55ced9288197</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI/MLOps Architect - R&amp;D IT</t>
+          <t>Java Full Stack Engineer - Professional</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Driscoll's</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Watsonville, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Git, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a566d06ed5f6179</t>
+          <t>https://www.indeed.com/viewjob?jk=1bae9430c620c785</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Data Lake, Snowflake, Redshift, Kafka, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Data Lake, Snowflake, Databricks, Kafka, Hadoop, MongoDB, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,102 +881,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
+          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior ML/LLM Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Renal Care</t>
+          <t>HealthStream</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Pinecone, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88b39030682b636</t>
+          <t>https://www.indeed.com/viewjob?jk=e9460595d63aeb80</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Backend Python Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3MD Inc.</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Glue, Athena, Jenkins, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe103858c74b7951</t>
+          <t>https://www.indeed.com/viewjob?jk=df4b1cc4ed807ce6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Research Scientist/Engineer</t>
+          <t>Software Engineer 2 (Java , SpringBoot, Micorservices)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EDDA TECHNOLOGY, INC.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Keras, Python, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,77 +986,637 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa77201670c86968</t>
+          <t>https://www.indeed.com/viewjob?jk=474e21e6184868bd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Intern- Software Engineer</t>
+          <t>Software Engineer 2 (Java , SpringBoot, Micorservices)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b946ca87ec47098e</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd1dfac7a1e46e4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Fall Co-op, Software Engineer</t>
+          <t>Software Engineer 2 (Java , SpringBoot, Micorservices)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=662992d2fea818bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Java , SpringBoot, Micorservices)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c429ac145f2975b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Java , SpringBoot, Micorservices)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=276863ff7972c545</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Java , SpringBoot, Micorservices)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6763fda2c11967fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Java , SpringBoot, Micorservices)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b3044ed301e647c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Java , SpringBoot, Micorservices)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brookfield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5295a8db6e31188e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Java , SpringBoot, Micorservices)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Gresham, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27a4593e9b507ff6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Java , SpringBoot, Micorservices)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Earth City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=293a6a748a5daa52</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Databricks, Matplotlib, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Scientist</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GE HealthCare</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Hadoop, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b81122084472689</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Lake, Kinesis, Kubernetes, Terraform, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=946eab65c2714d7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Lake, Kinesis, Kubernetes, Terraform, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54df8bbe8b75f939</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Analytics Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Butler Till</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Fullstack, Safety Experience</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac52f0877fad9d37</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Git, NoSQL, Python, SQL, R, Java, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66da552f497e7eed</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI Intern (Summer 2026)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>First Solar</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Perrysburg, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c7339225cd5bfa6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Engineer III, Machine Learning Software</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Git, Kafka, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83285bf7b029f1c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Investment Data Systems</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Arrowstreet Capital LP</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, S3, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4d2e2c577635db6</t>
         </is>
       </c>
     </row>
